--- a/artfynd/A 61913-2025 artfynd.xlsx
+++ b/artfynd/A 61913-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,56 +675,47 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>66920914</v>
+        <v>67492763</v>
       </c>
       <c r="B2" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vassaravaara NO, Lu lm</t>
+          <t>sorvanen, Lu lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>749741.0037014887</v>
+        <v>749886</v>
       </c>
       <c r="R2" t="n">
-        <v>7455416.938210358</v>
+        <v>7455392</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,124 +745,77 @@
           <t>2017-07-28</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-07-28</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>vanlig sälg</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Salix caprea subsp. caprea</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Salix caprea subsp. caprea</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Thorleif Joelson</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Thorleif Joelson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2017 Norrbotten</t>
-        </is>
-      </c>
+          <t>per-erik mukka, Bo karlstens, Thorleif Joelson, Evelina Lindgren</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>66920875</v>
+        <v>67490261</v>
       </c>
       <c r="B3" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91859</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>112</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Vassaravaara NO, Lu lm</t>
+          <t>sorvanen, Lu lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>749758.0094385248</v>
+        <v>749858</v>
       </c>
       <c r="R3" t="n">
-        <v>7455427.914083888</v>
+        <v>7455364</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -901,120 +845,81 @@
           <t>2017-07-28</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2017-07-28</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Blandsumpskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>vanlig sälg</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Salix caprea subsp. caprea</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea subsp. caprea</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Thorleif Joelson</t>
+          <t>per-erik mukka</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Thorleif Joelson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2017 Norrbotten</t>
-        </is>
-      </c>
+          <t>per-erik mukka, Bo karlstens, Evelina Lindgren, Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>66932602</v>
+        <v>66920875</v>
       </c>
       <c r="B4" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Vassaravaara NO, Lu lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>749741.0037014887</v>
+        <v>749758</v>
       </c>
       <c r="R4" t="n">
-        <v>7455416.938210358</v>
+        <v>7455428</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1044,54 +949,43 @@
           <t>2017-07-28</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2017-07-28</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Skogsmark</t>
+          <t>Blandsumpskog</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>vanlig gran</t>
+          <t>vanlig sälg</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Picea abies subsp. abies</t>
+          <t>Salix caprea subsp. caprea</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies subsp. abies</t>
+          <t>Bark on living woody plant # Salix caprea subsp. caprea</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1113,52 +1007,51 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>67490261</v>
+        <v>66920914</v>
       </c>
       <c r="B5" t="n">
-        <v>89338</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>112</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>sorvanen, Lu lm</t>
+          <t>Vassaravaara NO, Lu lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>749857.5758989833</v>
+        <v>749741</v>
       </c>
       <c r="R5" t="n">
-        <v>7455364.356366224</v>
+        <v>7455417</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1188,77 +1081,90 @@
           <t>2017-07-28</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2017-07-28</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>vanlig sälg</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Salix caprea subsp. caprea</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Salix caprea subsp. caprea</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>per-erik mukka</t>
+          <t>Thorleif Joelson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>per-erik mukka, Evelina Lindgren, Bo karlstens, Thorleif Joelson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2017 Norrbotten</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>67492763</v>
+        <v>67492873</v>
       </c>
       <c r="B6" t="n">
-        <v>89633</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>65</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1270,10 +1176,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>749886.3474618689</v>
+        <v>749801</v>
       </c>
       <c r="R6" t="n">
-        <v>7455392.086466345</v>
+        <v>7455433</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1303,28 +1209,17 @@
           <t>2017-07-28</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2017-07-28</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1336,22 +1231,21 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>per-erik mukka, Evelina Lindgren, Bo karlstens, Thorleif Joelson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>per-erik mukka, Bo karlstens, Thorleif Joelson, Evelina Lindgren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2017 Norrbotten</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>67492851</v>
+        <v>67492829</v>
       </c>
       <c r="B7" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106229</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,21 +1253,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221952</v>
+        <v>221725</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1386,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>749800.6733974108</v>
+        <v>749801</v>
       </c>
       <c r="R7" t="n">
-        <v>7455432.6629871</v>
+        <v>7455433</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1419,19 +1313,9 @@
           <t>2017-07-28</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2017-07-28</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1451,26 +1335,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>per-erik mukka, Evelina Lindgren, Bo karlstens, Thorleif Joelson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2017 Norrbotten</t>
-        </is>
-      </c>
+          <t>per-erik mukka, Bo karlstens, Thorleif Joelson, Evelina Lindgren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>67492829</v>
+        <v>67492851</v>
       </c>
       <c r="B8" t="n">
-        <v>103250</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1478,21 +1353,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221725</v>
+        <v>221952</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1505,10 +1380,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>749800.6733974108</v>
+        <v>749801</v>
       </c>
       <c r="R8" t="n">
-        <v>7455432.6629871</v>
+        <v>7455433</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1538,19 +1413,9 @@
           <t>2017-07-28</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2017-07-28</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1570,124 +1435,10 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>per-erik mukka, Evelina Lindgren, Bo karlstens, Thorleif Joelson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>67492873</v>
-      </c>
-      <c r="B9" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>6462</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Stuplav</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Nephroma bellum</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>sorvanen, Lu lm</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>749800.6733974108</v>
-      </c>
-      <c r="R9" t="n">
-        <v>7455432.6629871</v>
-      </c>
-      <c r="S9" t="n">
-        <v>10</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Gällivare</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Lule lappmark</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Gällivare</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2017-07-28</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2017-07-28</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>per-erik mukka</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>per-erik mukka, Evelina Lindgren, Bo karlstens, Thorleif Joelson</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
+          <t>per-erik mukka, Bo karlstens, Thorleif Joelson, Evelina Lindgren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2017 Norrbotten</t>
         </is>
